--- a/student_assessment_forms/007_mineral_science_knowledge_assessment--student_assessment_forms.xlsx
+++ b/student_assessment_forms/007_mineral_science_knowledge_assessment--student_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mineral Science Knowledge Assessment</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is the definition of geology</t>
+          <t>What is geology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Which of the following is the largest planet</t>
+          <t>Question 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is a rock that is formed from the cooling of Magma</t>
+          <t>What is the definition of a fossil</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the process of rocks being broken down by wind</t>
+          <t>What is the process of rocks being broken down by wind?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the process of rocks being broken down by wind</t>
+          <t>What is the process of rocks being broken down by ice?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the process of rocks being broken down by water</t>
+          <t>What is the process of rocks being broken down by heat?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the process of rocks being broken down by ice</t>
+          <t>What is the process of rocks being broken down by living organisms?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the process of rocks being broken down by heat</t>
+          <t>What is the definition of geologic time scale?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>question_9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is the process of rocks being broken down by living organisms</t>
+          <t>What is the process of geologic time scale?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>question_10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What is the process of rocks being broken down by humans</t>
+          <t>What is the definition of a mineral?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>question_11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What is the definition of a fossil</t>
+          <t>What is the definition of a gemstone?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,292 +796,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>question_12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What is the definition of a fossil</t>
+          <t>What is the definition of a rock?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>question_12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What is the definition of a fossil</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>question_13</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What is the definition of a Mineral</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>question_14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>What is geologic time scale</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>question_15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>What is geologic time scale</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>question_16</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What is geologic time scale</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_17</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What is geologic time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What is the process of geologic time scale</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What is geologic time scale</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What is geologic time scale</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What is geology</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What is geology</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What is geology</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,151 +850,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>earth</t>
+          <t>fossil</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Fossil</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>saturn</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>jupiter</t>
+          <t>gemstone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Jupiter</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>question_3_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>granite</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Granite</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>question_3_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>marble</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Marble</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>question_3_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>limestone</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Limestone</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>fossil</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Fossil</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>mineral</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Mineral</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>question_12_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>gemstone</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t>Gemstone</t>
         </is>
